--- a/public/DH_TechM_Managed_Services_BI_Source.xlsx
+++ b/public/DH_TechM_Managed_Services_BI_Source.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1037" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF2D934-A72B-4027-8C13-0BFE5FB5FDE6}"/>
+  <xr:revisionPtr revIDLastSave="1046" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93633DF2-0848-4A16-BA0E-1DD2D1EADC51}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="10" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Agenda" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,124 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="493">
+  <si>
+    <t>Agenda</t>
+  </si>
+  <si>
+    <t>Agenda_No</t>
+  </si>
+  <si>
+    <t>Agenda_Item</t>
+  </si>
+  <si>
+    <t>Minutes of Meeting : Last Meeting</t>
+  </si>
+  <si>
+    <t>IT Operations &amp; Service Management Dashboard – Apr to July</t>
+  </si>
+  <si>
+    <t>Autonomous Service Desk Operations</t>
+  </si>
+  <si>
+    <t>Automation : Progress Summary</t>
+  </si>
+  <si>
+    <t>Vulnerability Remediation : Progress Summary</t>
+  </si>
+  <si>
+    <t>Value Co creation: IT Infra</t>
+  </si>
+  <si>
+    <t>Value Co creation: IT Security</t>
+  </si>
+  <si>
+    <t>Pending Ticket Analysis</t>
+  </si>
+  <si>
+    <t>Projects &amp; Demand Support</t>
+  </si>
+  <si>
+    <t>Action Items</t>
+  </si>
+  <si>
+    <t>Action_No</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Type_Description</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Original_Due_Date</t>
+  </si>
+  <si>
+    <t>Revised_Due_Date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>New Contract commenced w.e.f 1st Apr’2026. Last two months MS support highlights and efforts consumed in value co-creation, presented by TechM Delivery Head (Sudesh)</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>TechM</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>TechM to present the Automation and AI Progress w.r.t 32 USE CASE presented during RFP defence proposal, in next review meeting.</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>On going</t>
+  </si>
+  <si>
+    <t>Included in deck</t>
+  </si>
+  <si>
+    <t>Patching through Qualys TOOL has been tested successfully. TechM to present the Qualys Patching status in next review meeting.</t>
+  </si>
+  <si>
+    <t>Project Progress included in deck.</t>
+  </si>
+  <si>
+    <t>TechM to present the Open Ticket Summary and Ticket Resolution Trend through Automation. Purpose is to review the progress</t>
+  </si>
+  <si>
+    <t>On Hold Tickets will be audited for proper justification and update compliance on ITSM TOOL</t>
+  </si>
+  <si>
+    <t>Pending Tickets Analysis updated in deck</t>
+  </si>
+  <si>
+    <t>Explore possibility to create single pane of glass using Azure Foundry capabilities, instead of multiple Power BI Dash-boards currently used for Operational purpose</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>03 Foundry SMEs on-boarded, USE CASE identification and approval in progress</t>
+  </si>
   <si>
     <t>Availability</t>
   </si>
@@ -377,12 +494,6 @@
   </si>
   <si>
     <t>Due Date</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Type</t>
   </si>
   <si>
     <t>Identified</t>
@@ -1075,18 +1186,12 @@
     <t>Accountability</t>
   </si>
   <si>
-    <t>Owner</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>Project Dependency</t>
   </si>
   <si>
@@ -1127,9 +1232,6 @@
   </si>
   <si>
     <t>Overdue Risk Count as on 26 Aug</t>
-  </si>
-  <si>
-    <t>Closed</t>
   </si>
   <si>
     <t>Vendor Dependency</t>
@@ -1748,9 +1850,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Remarks</t>
   </si>
   <si>
     <t>Total_Apr_Jul_USD</t>
@@ -2281,7 +2380,7 @@
     <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2526,23 +2625,8 @@
     <xf numFmtId="8" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="12" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2559,8 +2643,23 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="12" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2579,6 +2678,18 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
@@ -2924,9 +3035,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A3:B13"/>
+  <sheetFormatPr defaultColWidth="37.5703125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="37.5703125" style="63"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2">
+      <c r="A3" s="126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="126"/>
+    </row>
+    <row r="4" spans="1:2" ht="33">
+      <c r="A4" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="84">
+      <c r="A5" s="70">
+        <v>1</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="150.75">
+      <c r="A6" s="127">
+        <v>2</v>
+      </c>
+      <c r="B6" s="128" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="100.5">
+      <c r="A7" s="70">
+        <v>3</v>
+      </c>
+      <c r="B7" s="71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="84">
+      <c r="A8" s="127">
+        <v>4</v>
+      </c>
+      <c r="B8" s="128" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="117">
+      <c r="A9" s="70">
+        <v>5</v>
+      </c>
+      <c r="B9" s="71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="50.25">
+      <c r="A10" s="127">
+        <v>6</v>
+      </c>
+      <c r="B10" s="128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="66.75">
+      <c r="A11" s="70">
+        <v>7</v>
+      </c>
+      <c r="B11" s="71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="50.25">
+      <c r="A12" s="127">
+        <v>8</v>
+      </c>
+      <c r="B12" s="128" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="66.75">
+      <c r="A13" s="70">
+        <v>9</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:B3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2942,14 +3146,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="18">
-      <c r="A2" s="108" t="s">
-        <v>377</v>
-      </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+      <c r="A2" s="119" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
       <c r="F2" s="125" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="G2" s="125"/>
       <c r="H2" s="125"/>
@@ -2960,40 +3164,40 @@
     </row>
     <row r="3" spans="1:17" ht="16.5">
       <c r="A3" s="68" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="B3" s="69" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="D3" s="69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>379</v>
-      </c>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="M3" s="108" t="s">
-        <v>380</v>
-      </c>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
+        <v>45</v>
+      </c>
+      <c r="F3" s="119" t="s">
+        <v>413</v>
+      </c>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="M3" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="N3" s="119"/>
+      <c r="O3" s="119"/>
       <c r="Q3" s="67" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="50.25">
       <c r="A4" s="70" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="C4" s="71">
         <v>23</v>
@@ -3002,42 +3206,42 @@
         <v>46204</v>
       </c>
       <c r="F4" s="68" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="H4" s="69" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="I4" s="69" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="J4" s="69" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="K4" s="69" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="M4" s="68" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="N4" s="69" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="O4" s="69" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="Q4" s="68" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="84">
       <c r="A5" s="74" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="B5" s="75" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="C5" s="75">
         <v>1</v>
@@ -3046,7 +3250,7 @@
         <v>46204</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="G5" s="71">
         <v>24</v>
@@ -3064,24 +3268,24 @@
         <v>46304</v>
       </c>
       <c r="M5" s="70" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="N5" s="71" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="O5" s="71">
         <v>1</v>
       </c>
       <c r="Q5" s="70" t="s">
-        <v>397</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="84">
       <c r="A6" s="70" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="C6" s="71">
         <v>22</v>
@@ -3090,10 +3294,10 @@
         <v>46204</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="N6" s="75" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="O6" s="75">
         <v>2</v>
@@ -3101,10 +3305,10 @@
     </row>
     <row r="7" spans="1:17" ht="50.25">
       <c r="A7" s="74" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="B7" s="75" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="C7" s="75">
         <v>70</v>
@@ -3113,10 +3317,10 @@
         <v>46204</v>
       </c>
       <c r="M7" s="70" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="N7" s="71" t="s">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="O7" s="71">
         <v>3</v>
@@ -3124,10 +3328,10 @@
     </row>
     <row r="8" spans="1:17" ht="66.75">
       <c r="A8" s="70" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="C8" s="71">
         <v>30</v>
@@ -3136,10 +3340,10 @@
         <v>46204</v>
       </c>
       <c r="M8" s="74" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="N8" s="75" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="O8" s="75">
         <v>4</v>
@@ -3147,10 +3351,10 @@
     </row>
     <row r="9" spans="1:17" ht="100.5">
       <c r="A9" s="74" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="B9" s="75" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="C9" s="75">
         <v>1</v>
@@ -3159,10 +3363,10 @@
         <v>46204</v>
       </c>
       <c r="M9" s="70" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="N9" s="71" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="O9" s="71">
         <v>5</v>
@@ -3170,10 +3374,10 @@
     </row>
     <row r="10" spans="1:17" ht="33.75">
       <c r="A10" s="70" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="C10" s="71">
         <v>4</v>
@@ -3182,10 +3386,10 @@
         <v>46204</v>
       </c>
       <c r="M10" s="74" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="N10" s="75" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="O10" s="75">
         <v>6</v>
@@ -3193,10 +3397,10 @@
     </row>
     <row r="11" spans="1:17" ht="66.75">
       <c r="A11" s="74" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="B11" s="75" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="C11" s="75">
         <v>13</v>
@@ -3205,10 +3409,10 @@
         <v>46204</v>
       </c>
       <c r="M11" s="70" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="N11" s="71" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="O11" s="71">
         <v>7</v>
@@ -3220,10 +3424,10 @@
       <c r="C12" s="80"/>
       <c r="D12" s="80"/>
       <c r="M12" s="74" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N12" s="75" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="O12" s="75">
         <v>1</v>
@@ -3231,16 +3435,16 @@
     </row>
     <row r="13" spans="1:17" ht="84">
       <c r="A13" s="124" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="B13" s="124"/>
       <c r="C13" s="124"/>
       <c r="D13" s="124"/>
       <c r="M13" s="70" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N13" s="71" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="O13" s="71">
         <v>2</v>
@@ -3248,22 +3452,22 @@
     </row>
     <row r="14" spans="1:17" ht="66.75">
       <c r="A14" s="68" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="B14" s="69" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="C14" s="69" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="D14" s="69" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="M14" s="74" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N14" s="75" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="O14" s="75">
         <v>3</v>
@@ -3271,10 +3475,10 @@
     </row>
     <row r="15" spans="1:17" ht="134.25">
       <c r="A15" s="70" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="C15" s="71">
         <v>8</v>
@@ -3283,10 +3487,10 @@
         <v>46295</v>
       </c>
       <c r="M15" s="70" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N15" s="71" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="O15" s="71">
         <v>4</v>
@@ -3294,10 +3498,10 @@
     </row>
     <row r="16" spans="1:17" ht="117">
       <c r="A16" s="74" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="B16" s="75" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="C16" s="75">
         <v>12</v>
@@ -3306,10 +3510,10 @@
         <v>46265</v>
       </c>
       <c r="M16" s="74" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N16" s="75" t="s">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="O16" s="75">
         <v>5</v>
@@ -3317,10 +3521,10 @@
     </row>
     <row r="17" spans="1:15" ht="117">
       <c r="A17" s="70" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="C17" s="71">
         <v>12</v>
@@ -3329,10 +3533,10 @@
         <v>46325</v>
       </c>
       <c r="M17" s="70" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N17" s="71" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="O17" s="71">
         <v>6</v>
@@ -3340,20 +3544,20 @@
     </row>
     <row r="18" spans="1:15" ht="117">
       <c r="A18" s="74" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="B18" s="75" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="C18" s="75">
         <v>4</v>
       </c>
       <c r="D18" s="75"/>
       <c r="M18" s="74" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N18" s="75" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="O18" s="75">
         <v>7</v>
@@ -3361,10 +3565,10 @@
     </row>
     <row r="19" spans="1:15" ht="66.75">
       <c r="M19" s="70" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N19" s="71" t="s">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="O19" s="71">
         <v>8</v>
@@ -3372,10 +3576,10 @@
     </row>
     <row r="20" spans="1:15" ht="66.75">
       <c r="M20" s="74" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N20" s="75" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="O20" s="75">
         <v>9</v>
@@ -3383,10 +3587,10 @@
     </row>
     <row r="21" spans="1:15" ht="84">
       <c r="M21" s="70" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N21" s="71" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="O21" s="71">
         <v>10</v>
@@ -3394,10 +3598,10 @@
     </row>
     <row r="22" spans="1:15" ht="50.25">
       <c r="M22" s="74" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N22" s="75" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="O22" s="75">
         <v>11</v>
@@ -3405,10 +3609,10 @@
     </row>
     <row r="23" spans="1:15" ht="66.75">
       <c r="M23" s="70" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N23" s="71" t="s">
-        <v>430</v>
+        <v>464</v>
       </c>
       <c r="O23" s="71">
         <v>12</v>
@@ -3416,10 +3620,10 @@
     </row>
     <row r="24" spans="1:15" ht="66.75">
       <c r="M24" s="74" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N24" s="75" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="O24" s="75">
         <v>13</v>
@@ -3446,103 +3650,103 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:25">
-      <c r="A3" s="108" t="s">
-        <v>432</v>
-      </c>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="M3" s="108" t="s">
-        <v>433</v>
-      </c>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="108"/>
-      <c r="T3" s="108" t="s">
-        <v>434</v>
-      </c>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
-      <c r="X3" s="108" t="s">
-        <v>435</v>
-      </c>
-      <c r="Y3" s="108"/>
+      <c r="A3" s="119" t="s">
+        <v>466</v>
+      </c>
+      <c r="B3" s="119"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="M3" s="119" t="s">
+        <v>467</v>
+      </c>
+      <c r="N3" s="119"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="119"/>
+      <c r="Q3" s="119"/>
+      <c r="R3" s="119"/>
+      <c r="T3" s="119" t="s">
+        <v>468</v>
+      </c>
+      <c r="U3" s="119"/>
+      <c r="V3" s="119"/>
+      <c r="X3" s="119" t="s">
+        <v>469</v>
+      </c>
+      <c r="Y3" s="119"/>
     </row>
     <row r="4" spans="1:25" ht="83.25">
       <c r="A4" s="68" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>437</v>
+        <v>471</v>
       </c>
       <c r="E4" s="69" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="F4" s="69" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="G4" s="69" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="H4" s="69" t="s">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="I4" s="69" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="J4" s="69" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="K4" s="69" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="M4" s="68" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="N4" s="69" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="O4" s="69" t="s">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="P4" s="69" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="Q4" s="69" t="s">
-        <v>447</v>
+        <v>481</v>
       </c>
       <c r="R4" s="69" t="s">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="T4" s="68" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="U4" s="69" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="V4" s="69" t="s">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="X4" s="68" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="Y4" s="69" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="409.6">
@@ -3550,13 +3754,13 @@
         <v>46113</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D5" s="71" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E5" s="71">
         <v>40</v>
@@ -3583,28 +3787,28 @@
         <v>46113</v>
       </c>
       <c r="N5" s="71" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="O5" s="71" t="s">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="P5" s="71">
         <v>31200</v>
       </c>
       <c r="Q5" s="71" t="s">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="R5" s="71" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
       <c r="T5" s="70" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="U5" s="71">
         <v>454428</v>
       </c>
       <c r="V5" s="71" t="s">
-        <v>455</v>
+        <v>488</v>
       </c>
       <c r="X5" s="81">
         <v>46113</v>
@@ -3618,13 +3822,13 @@
         <v>46113</v>
       </c>
       <c r="B6" s="75" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="E6" s="75">
         <v>94</v>
@@ -3651,10 +3855,10 @@
         <v>46143</v>
       </c>
       <c r="N6" s="75" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="O6" s="75" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="P6" s="75">
         <v>0</v>
@@ -3662,13 +3866,13 @@
       <c r="Q6" s="75"/>
       <c r="R6" s="75"/>
       <c r="T6" s="74" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="U6" s="75">
         <v>31200</v>
       </c>
       <c r="V6" s="75" t="s">
-        <v>457</v>
+        <v>490</v>
       </c>
       <c r="X6" s="82">
         <v>46143</v>
@@ -3682,13 +3886,13 @@
         <v>46143</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C7" s="71" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D7" s="71" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E7" s="71">
         <v>49</v>
@@ -3715,10 +3919,10 @@
         <v>46174</v>
       </c>
       <c r="N7" s="71" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="O7" s="71" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="P7" s="71">
         <v>0</v>
@@ -3737,13 +3941,13 @@
         <v>46143</v>
       </c>
       <c r="B8" s="75" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="E8" s="75">
         <v>21</v>
@@ -3770,10 +3974,10 @@
         <v>46204</v>
       </c>
       <c r="N8" s="75" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="O8" s="75" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="P8" s="75">
         <v>0</v>
@@ -3792,13 +3996,13 @@
         <v>46174</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C9" s="71" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E9" s="71">
         <v>38</v>
@@ -3822,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="X9" s="70" t="s">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="Y9" s="71">
         <v>485628</v>
@@ -3833,13 +4037,13 @@
         <v>46174</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C10" s="75" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D10" s="75" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="E10" s="75">
         <v>71</v>
@@ -3868,13 +4072,13 @@
         <v>46174</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C11" s="71" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D11" s="71" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="E11" s="71">
         <v>40</v>
@@ -3903,13 +4107,13 @@
         <v>46204</v>
       </c>
       <c r="B12" s="75" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C12" s="75" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E12" s="75">
         <v>533</v>
@@ -3938,13 +4142,13 @@
         <v>46204</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C13" s="71" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="E13" s="71">
         <v>20</v>
@@ -3973,13 +4177,13 @@
         <v>46204</v>
       </c>
       <c r="B14" s="75" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C14" s="75" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="D14" s="75" t="s">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="E14" s="75">
         <v>151</v>
@@ -4016,9 +4220,217 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C125684B-CF16-4886-8A5D-34B5ACFB5E40}">
-  <dimension ref="A1"/>
+  <dimension ref="A2:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="1:9">
+      <c r="A2" s="126" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+    </row>
+    <row r="3" spans="1:9" ht="50.25">
+      <c r="A3" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="69" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="409.6">
+      <c r="A4" s="70">
+        <v>1</v>
+      </c>
+      <c r="B4" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="73">
+        <v>46202</v>
+      </c>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="71"/>
+    </row>
+    <row r="5" spans="1:9" ht="318">
+      <c r="A5" s="127">
+        <v>2</v>
+      </c>
+      <c r="B5" s="128" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="129">
+        <v>46230</v>
+      </c>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="128" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="318">
+      <c r="A6" s="70">
+        <v>3</v>
+      </c>
+      <c r="B6" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="73">
+        <v>46230</v>
+      </c>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="318">
+      <c r="A7" s="127">
+        <v>4</v>
+      </c>
+      <c r="B7" s="128" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="129">
+        <v>46230</v>
+      </c>
+      <c r="G7" s="128"/>
+      <c r="H7" s="128" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="128" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="216.75">
+      <c r="A8" s="70">
+        <v>5</v>
+      </c>
+      <c r="B8" s="71" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="73">
+        <v>46230</v>
+      </c>
+      <c r="G8" s="71"/>
+      <c r="H8" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="71" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="384.75">
+      <c r="A9" s="127">
+        <v>6</v>
+      </c>
+      <c r="B9" s="128" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="128" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="129">
+        <v>46230</v>
+      </c>
+      <c r="G9" s="129">
+        <v>46295</v>
+      </c>
+      <c r="H9" s="128" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="128" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4048,96 +4460,96 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:37">
-      <c r="C2" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="I2" s="111" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="O2" s="113" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="V2" s="114" t="s">
-        <v>3</v>
-      </c>
-      <c r="W2" s="114"/>
-      <c r="AA2" s="115" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
-      <c r="AE2" s="116"/>
-      <c r="AF2" s="117"/>
-      <c r="AJ2" s="118" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK2" s="118"/>
+      <c r="C2" s="114" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="I2" s="115" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="O2" s="117" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="V2" s="109" t="s">
+        <v>42</v>
+      </c>
+      <c r="W2" s="109"/>
+      <c r="AA2" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" s="111"/>
+      <c r="AC2" s="111"/>
+      <c r="AD2" s="111"/>
+      <c r="AE2" s="111"/>
+      <c r="AF2" s="112"/>
+      <c r="AJ2" s="113" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK2" s="113"/>
     </row>
     <row r="3" spans="2:37">
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="10" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="V3" s="11"/>
       <c r="W3" s="18" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="AA3" s="15"/>
       <c r="AB3" s="19" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="AC3" s="19" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="AD3" s="19" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="AE3" s="19" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AF3" s="19" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="AJ3" s="20" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="AK3" s="20" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:37">
-      <c r="B4" s="109" t="s">
-        <v>20</v>
+      <c r="B4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="C4" s="21">
         <v>46138</v>
@@ -4148,8 +4560,8 @@
       <c r="E4" s="3">
         <v>0.99</v>
       </c>
-      <c r="H4" s="109" t="s">
-        <v>20</v>
+      <c r="H4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="I4" s="23">
         <v>46138</v>
@@ -4160,8 +4572,8 @@
       <c r="K4" s="5">
         <v>4.5</v>
       </c>
-      <c r="N4" s="109" t="s">
-        <v>20</v>
+      <c r="N4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="O4" s="25">
         <v>46138</v>
@@ -4176,8 +4588,8 @@
         <f>P4/(P4+Q4)</f>
         <v>0.96</v>
       </c>
-      <c r="U4" s="109" t="s">
-        <v>20</v>
+      <c r="U4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="V4" s="13">
         <v>46138</v>
@@ -4185,8 +4597,8 @@
       <c r="W4" s="12">
         <v>2</v>
       </c>
-      <c r="Z4" s="109" t="s">
-        <v>20</v>
+      <c r="Z4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="AA4" s="16">
         <v>46138</v>
@@ -4206,18 +4618,18 @@
       <c r="AF4" s="14">
         <v>3</v>
       </c>
-      <c r="AI4" s="109" t="s">
-        <v>21</v>
+      <c r="AI4" s="108" t="s">
+        <v>60</v>
       </c>
       <c r="AJ4" s="17">
         <v>1</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:37">
-      <c r="B5" s="109"/>
+      <c r="B5" s="108"/>
       <c r="C5" s="21">
         <v>46168</v>
       </c>
@@ -4227,7 +4639,7 @@
       <c r="E5" s="3">
         <v>0.99</v>
       </c>
-      <c r="H5" s="109"/>
+      <c r="H5" s="108"/>
       <c r="I5" s="23">
         <v>46168</v>
       </c>
@@ -4237,7 +4649,7 @@
       <c r="K5" s="5">
         <v>4.5</v>
       </c>
-      <c r="N5" s="109"/>
+      <c r="N5" s="108"/>
       <c r="O5" s="25">
         <v>46168</v>
       </c>
@@ -4251,14 +4663,14 @@
         <f t="shared" ref="R5:R9" si="0">P5/(P5+Q5)</f>
         <v>0.94</v>
       </c>
-      <c r="U5" s="109"/>
+      <c r="U5" s="108"/>
       <c r="V5" s="13">
         <v>46168</v>
       </c>
       <c r="W5" s="12">
         <v>0</v>
       </c>
-      <c r="Z5" s="109"/>
+      <c r="Z5" s="108"/>
       <c r="AA5" s="16">
         <v>46168</v>
       </c>
@@ -4277,16 +4689,16 @@
       <c r="AF5" s="14">
         <v>3</v>
       </c>
-      <c r="AI5" s="109"/>
+      <c r="AI5" s="108"/>
       <c r="AJ5" s="17">
         <v>2</v>
       </c>
       <c r="AK5" s="17" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="2:37">
-      <c r="B6" s="109"/>
+      <c r="B6" s="108"/>
       <c r="C6" s="21">
         <v>46199</v>
       </c>
@@ -4296,7 +4708,7 @@
       <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="109"/>
+      <c r="H6" s="108"/>
       <c r="I6" s="23">
         <v>46199</v>
       </c>
@@ -4306,7 +4718,7 @@
       <c r="K6" s="5">
         <v>4.5</v>
       </c>
-      <c r="N6" s="109"/>
+      <c r="N6" s="108"/>
       <c r="O6" s="25">
         <v>46199</v>
       </c>
@@ -4320,14 +4732,14 @@
         <f t="shared" si="0"/>
         <v>0.96</v>
       </c>
-      <c r="U6" s="109"/>
+      <c r="U6" s="108"/>
       <c r="V6" s="13">
         <v>46199</v>
       </c>
       <c r="W6" s="12">
         <v>0</v>
       </c>
-      <c r="Z6" s="109"/>
+      <c r="Z6" s="108"/>
       <c r="AA6" s="16">
         <v>46199</v>
       </c>
@@ -4346,16 +4758,16 @@
       <c r="AF6" s="14">
         <v>6</v>
       </c>
-      <c r="AI6" s="109"/>
+      <c r="AI6" s="108"/>
       <c r="AJ6" s="17">
         <v>3</v>
       </c>
       <c r="AK6" s="17" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="2:37">
-      <c r="B7" s="109"/>
+      <c r="B7" s="108"/>
       <c r="C7" s="21">
         <v>46229</v>
       </c>
@@ -4365,7 +4777,7 @@
       <c r="E7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="109"/>
+      <c r="H7" s="108"/>
       <c r="I7" s="23">
         <v>46229</v>
       </c>
@@ -4375,7 +4787,7 @@
       <c r="K7" s="5">
         <v>4.5</v>
       </c>
-      <c r="N7" s="109"/>
+      <c r="N7" s="108"/>
       <c r="O7" s="25">
         <v>46229</v>
       </c>
@@ -4389,14 +4801,14 @@
         <f t="shared" si="0"/>
         <v>0.97</v>
       </c>
-      <c r="U7" s="109"/>
+      <c r="U7" s="108"/>
       <c r="V7" s="13">
         <v>46229</v>
       </c>
       <c r="W7" s="12">
         <v>1</v>
       </c>
-      <c r="Z7" s="109"/>
+      <c r="Z7" s="108"/>
       <c r="AA7" s="16">
         <v>46229</v>
       </c>
@@ -4415,16 +4827,16 @@
       <c r="AF7" s="14">
         <v>3</v>
       </c>
-      <c r="AI7" s="109"/>
+      <c r="AI7" s="108"/>
       <c r="AJ7" s="17">
         <v>4</v>
       </c>
       <c r="AK7" s="17" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="2:37">
-      <c r="B8" s="109"/>
+      <c r="B8" s="108"/>
       <c r="C8" s="22">
         <v>46260</v>
       </c>
@@ -4434,7 +4846,7 @@
       <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="109"/>
+      <c r="H8" s="108"/>
       <c r="I8" s="24">
         <v>46260</v>
       </c>
@@ -4444,7 +4856,7 @@
       <c r="K8" s="5">
         <v>4.5</v>
       </c>
-      <c r="N8" s="109"/>
+      <c r="N8" s="108"/>
       <c r="O8" s="25">
         <v>46260</v>
       </c>
@@ -4458,14 +4870,14 @@
         <f t="shared" si="0"/>
         <v>0.96</v>
       </c>
-      <c r="U8" s="109"/>
+      <c r="U8" s="108"/>
       <c r="V8" s="13">
         <v>46260</v>
       </c>
       <c r="W8" s="12">
         <v>0</v>
       </c>
-      <c r="Z8" s="109"/>
+      <c r="Z8" s="108"/>
       <c r="AA8" s="16">
         <v>46260</v>
       </c>
@@ -4484,14 +4896,14 @@
       <c r="AF8" s="14">
         <v>3</v>
       </c>
-      <c r="AI8" s="109"/>
+      <c r="AI8" s="108"/>
       <c r="AJ8" s="17">
         <v>5</v>
       </c>
       <c r="AK8" s="17"/>
     </row>
     <row r="9" spans="2:37">
-      <c r="B9" s="109"/>
+      <c r="B9" s="108"/>
       <c r="C9" s="22">
         <v>46291</v>
       </c>
@@ -4501,7 +4913,7 @@
       <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="109"/>
+      <c r="H9" s="108"/>
       <c r="I9" s="24">
         <v>46291</v>
       </c>
@@ -4511,7 +4923,7 @@
       <c r="K9" s="5">
         <v>4.5</v>
       </c>
-      <c r="N9" s="109"/>
+      <c r="N9" s="108"/>
       <c r="O9" s="25">
         <v>46291</v>
       </c>
@@ -4525,14 +4937,14 @@
         <f t="shared" si="0"/>
         <v>0.98</v>
       </c>
-      <c r="U9" s="109"/>
+      <c r="U9" s="108"/>
       <c r="V9" s="13">
         <v>46291</v>
       </c>
       <c r="W9" s="12">
         <v>1</v>
       </c>
-      <c r="Z9" s="109"/>
+      <c r="Z9" s="108"/>
       <c r="AA9" s="16">
         <v>46291</v>
       </c>
@@ -4551,18 +4963,18 @@
       <c r="AF9" s="14">
         <v>6</v>
       </c>
-      <c r="AI9" s="109"/>
+      <c r="AI9" s="108"/>
       <c r="AJ9" s="17">
         <v>6</v>
       </c>
       <c r="AK9" s="17"/>
     </row>
     <row r="10" spans="2:37">
-      <c r="O10" s="112" t="s">
-        <v>26</v>
-      </c>
-      <c r="P10" s="112"/>
-      <c r="Q10" s="112"/>
+      <c r="O10" s="116" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
       <c r="R10" s="9">
         <f>AVERAGE(R4:R9)</f>
         <v>0.96166666666666656</v>
@@ -4576,12 +4988,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="U4:U9"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="Z4:Z9"/>
-    <mergeCell ref="AA2:AF2"/>
-    <mergeCell ref="AJ2:AK2"/>
-    <mergeCell ref="AI4:AI9"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="H4:H9"/>
@@ -4589,6 +4995,12 @@
     <mergeCell ref="O10:Q10"/>
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="N4:N9"/>
+    <mergeCell ref="U4:U9"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="Z4:Z9"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AJ2:AK2"/>
+    <mergeCell ref="AI4:AI9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4624,80 +5036,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:42">
-      <c r="AE1" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF1" s="108"/>
-      <c r="AG1" s="108"/>
-      <c r="AH1" s="108"/>
+      <c r="AE1" s="119" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
       <c r="AI1" s="63"/>
-      <c r="AJ1" s="108" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK1" s="108"/>
-      <c r="AL1" s="108"/>
-      <c r="AM1" s="108"/>
-      <c r="AN1" s="108"/>
+      <c r="AJ1" s="119" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK1" s="119"/>
+      <c r="AL1" s="119"/>
+      <c r="AM1" s="119"/>
+      <c r="AN1" s="119"/>
       <c r="AO1" s="63"/>
       <c r="AP1" s="63"/>
     </row>
     <row r="2" spans="2:42" ht="50.25">
-      <c r="C2" s="119" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="H2" s="119" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="M2" s="119" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="R2" s="119" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="W2" s="119" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" s="119"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="119"/>
+      <c r="C2" s="118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="H2" s="118" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="M2" s="118" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="R2" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="S2" s="118"/>
+      <c r="T2" s="118"/>
+      <c r="W2" s="118" t="s">
+        <v>72</v>
+      </c>
+      <c r="X2" s="118"/>
+      <c r="Y2" s="118"/>
+      <c r="Z2" s="118"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="118"/>
       <c r="AE2" s="68" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="AF2" s="69" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="AG2" s="69" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AH2" s="69" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AI2" s="63"/>
       <c r="AJ2" s="68" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="AK2" s="69" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AL2" s="69" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="AM2" s="69" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="AN2" s="69" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="AO2" s="63"/>
       <c r="AP2" s="63"/>
@@ -4705,77 +5117,77 @@
     <row r="3" spans="2:42" ht="134.25">
       <c r="C3" s="99"/>
       <c r="D3" s="100" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="E3" s="100" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="H3" s="100" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="I3" s="100" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="J3" s="100" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="M3" s="100" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="N3" s="100" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="O3" s="100" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="R3" s="100" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="S3" s="100" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="T3" s="100" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="W3" s="100" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="X3" s="100" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="100" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="Z3" s="100" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="AA3" s="100" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="AB3" s="100" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="AC3" s="100" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AE3" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF3" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG3" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH3" s="71">
         <v>9</v>
       </c>
       <c r="AI3" s="63"/>
       <c r="AJ3" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AK3" s="71" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="AL3" s="71">
         <v>5</v>
@@ -4784,14 +5196,14 @@
         <v>50</v>
       </c>
       <c r="AN3" s="71" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="AO3" s="63"/>
       <c r="AP3" s="63"/>
     </row>
     <row r="4" spans="2:42" ht="150.75">
-      <c r="B4" s="109" t="s">
-        <v>20</v>
+      <c r="B4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="C4" s="101">
         <v>46138</v>
@@ -4802,11 +5214,11 @@
       <c r="E4" s="102">
         <v>6519</v>
       </c>
-      <c r="G4" s="109" t="s">
-        <v>20</v>
+      <c r="G4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="H4" s="99" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="I4" s="103">
         <v>637</v>
@@ -4814,35 +5226,35 @@
       <c r="J4" s="103">
         <v>1439</v>
       </c>
-      <c r="L4" s="109" t="s">
-        <v>20</v>
+      <c r="L4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="M4" s="103">
         <v>1</v>
       </c>
       <c r="N4" s="103" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="O4" s="103">
         <v>2577</v>
       </c>
-      <c r="Q4" s="109" t="s">
-        <v>20</v>
+      <c r="Q4" s="108" t="s">
+        <v>59</v>
       </c>
       <c r="R4" s="103">
         <v>1</v>
       </c>
       <c r="S4" s="103" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="T4" s="103">
         <v>3717</v>
       </c>
       <c r="W4" s="42" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="X4" s="42" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="Y4" s="42">
         <v>3703</v>
@@ -4861,10 +5273,10 @@
         <v>8402</v>
       </c>
       <c r="AE4" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF4" s="75" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG4" s="96">
         <v>46086</v>
@@ -4874,10 +5286,10 @@
       </c>
       <c r="AI4" s="63"/>
       <c r="AJ4" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AK4" s="75" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="AL4" s="75">
         <v>3</v>
@@ -4886,13 +5298,13 @@
         <v>30</v>
       </c>
       <c r="AN4" s="75" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="AO4" s="63"/>
       <c r="AP4" s="63"/>
     </row>
     <row r="5" spans="2:42" ht="134.25">
-      <c r="B5" s="109"/>
+      <c r="B5" s="108"/>
       <c r="C5" s="101">
         <v>46168</v>
       </c>
@@ -4902,9 +5314,9 @@
       <c r="E5" s="102">
         <v>4340</v>
       </c>
-      <c r="G5" s="109"/>
+      <c r="G5" s="108"/>
       <c r="H5" s="99" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="I5" s="103">
         <v>4283</v>
@@ -4912,31 +5324,31 @@
       <c r="J5" s="103">
         <v>5086</v>
       </c>
-      <c r="L5" s="109"/>
+      <c r="L5" s="108"/>
       <c r="M5" s="103">
         <v>2</v>
       </c>
       <c r="N5" s="103" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="O5" s="103">
         <v>690</v>
       </c>
-      <c r="Q5" s="109"/>
+      <c r="Q5" s="108"/>
       <c r="R5" s="103">
         <v>2</v>
       </c>
       <c r="S5" s="103" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="T5" s="103">
         <v>2249</v>
       </c>
       <c r="AE5" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF5" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG5" s="97">
         <v>46152</v>
@@ -4946,10 +5358,10 @@
       </c>
       <c r="AI5" s="63"/>
       <c r="AJ5" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AK5" s="71" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="AL5" s="71">
         <v>1</v>
@@ -4958,13 +5370,13 @@
         <v>10</v>
       </c>
       <c r="AN5" s="71" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="AO5" s="63"/>
       <c r="AP5" s="63"/>
     </row>
     <row r="6" spans="2:42" ht="117">
-      <c r="B6" s="109"/>
+      <c r="B6" s="108"/>
       <c r="C6" s="101">
         <v>46199</v>
       </c>
@@ -4974,9 +5386,9 @@
       <c r="E6" s="102">
         <v>5882</v>
       </c>
-      <c r="G6" s="109"/>
+      <c r="G6" s="108"/>
       <c r="H6" s="99" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="I6" s="103">
         <v>69</v>
@@ -4984,31 +5396,31 @@
       <c r="J6" s="103">
         <v>1353</v>
       </c>
-      <c r="L6" s="109"/>
+      <c r="L6" s="108"/>
       <c r="M6" s="103">
         <v>3</v>
       </c>
       <c r="N6" s="103" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="O6" s="103">
         <v>375</v>
       </c>
-      <c r="Q6" s="109"/>
+      <c r="Q6" s="108"/>
       <c r="R6" s="103">
         <v>3</v>
       </c>
       <c r="S6" s="103" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="T6" s="103">
         <v>1778</v>
       </c>
       <c r="AE6" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF6" s="75" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG6" s="96">
         <v>46315</v>
@@ -5018,10 +5430,10 @@
       </c>
       <c r="AI6" s="63"/>
       <c r="AJ6" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AK6" s="75" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AL6" s="75">
         <v>1</v>
@@ -5030,13 +5442,13 @@
         <v>10</v>
       </c>
       <c r="AN6" s="75" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="AO6" s="63"/>
       <c r="AP6" s="63"/>
     </row>
     <row r="7" spans="2:42" ht="66.75">
-      <c r="B7" s="109"/>
+      <c r="B7" s="108"/>
       <c r="C7" s="101">
         <v>46229</v>
       </c>
@@ -5046,9 +5458,9 @@
       <c r="E7" s="102">
         <v>5578</v>
       </c>
-      <c r="G7" s="109"/>
+      <c r="G7" s="108"/>
       <c r="H7" s="99" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="I7" s="103">
         <v>498</v>
@@ -5056,44 +5468,44 @@
       <c r="J7" s="103">
         <v>14441</v>
       </c>
-      <c r="L7" s="109"/>
+      <c r="L7" s="108"/>
       <c r="M7" s="103">
         <v>4</v>
       </c>
       <c r="N7" s="103" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="O7" s="103">
         <v>192</v>
       </c>
-      <c r="Q7" s="109"/>
+      <c r="Q7" s="108"/>
       <c r="R7" s="103">
         <v>4</v>
       </c>
       <c r="S7" s="103" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="T7" s="103">
         <v>1657</v>
       </c>
       <c r="AE7" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF7" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG7" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH7" s="71">
         <v>0</v>
       </c>
       <c r="AI7" s="63"/>
       <c r="AJ7" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AK7" s="71" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AL7" s="71">
         <v>21</v>
@@ -5102,13 +5514,13 @@
         <v>38</v>
       </c>
       <c r="AN7" s="71" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="AO7" s="63"/>
       <c r="AP7" s="63"/>
     </row>
     <row r="8" spans="2:42" ht="234">
-      <c r="B8" s="109"/>
+      <c r="B8" s="108"/>
       <c r="C8" s="101">
         <v>46260</v>
       </c>
@@ -5118,9 +5530,9 @@
       <c r="E8" s="102">
         <v>0</v>
       </c>
-      <c r="G8" s="109"/>
+      <c r="G8" s="108"/>
       <c r="H8" s="104" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="I8" s="104">
         <f>SUM(I4:I7)</f>
@@ -5130,44 +5542,44 @@
         <f>SUM(J4:J7)</f>
         <v>22319</v>
       </c>
-      <c r="L8" s="109"/>
+      <c r="L8" s="108"/>
       <c r="M8" s="103">
         <v>5</v>
       </c>
       <c r="N8" s="103" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="O8" s="103">
         <v>173</v>
       </c>
-      <c r="Q8" s="109"/>
+      <c r="Q8" s="108"/>
       <c r="R8" s="103">
         <v>5</v>
       </c>
       <c r="S8" s="103" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="T8" s="103">
         <v>1183</v>
       </c>
       <c r="AE8" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF8" s="75" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG8" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH8" s="75">
         <v>0</v>
       </c>
       <c r="AI8" s="63"/>
       <c r="AJ8" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AK8" s="75" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="AL8" s="75">
         <v>18</v>
@@ -5176,13 +5588,13 @@
         <v>33</v>
       </c>
       <c r="AN8" s="75" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="AO8" s="63"/>
       <c r="AP8" s="63"/>
     </row>
     <row r="9" spans="2:42" ht="200.25">
-      <c r="B9" s="109"/>
+      <c r="B9" s="108"/>
       <c r="C9" s="101">
         <v>46291</v>
       </c>
@@ -5194,23 +5606,23 @@
       </c>
       <c r="G9" s="89"/>
       <c r="AE9" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF9" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG9" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH9" s="71">
         <v>15</v>
       </c>
       <c r="AI9" s="63"/>
       <c r="AJ9" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AK9" s="71" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="AL9" s="71">
         <v>11</v>
@@ -5219,14 +5631,14 @@
         <v>20</v>
       </c>
       <c r="AN9" s="71" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="AO9" s="63"/>
       <c r="AP9" s="63"/>
     </row>
     <row r="10" spans="2:42" ht="117">
       <c r="C10" s="104" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="D10" s="105">
         <f>SUM(D4:D9)</f>
@@ -5237,23 +5649,23 @@
         <v>22319</v>
       </c>
       <c r="AE10" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF10" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG10" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH10" s="75">
         <v>7</v>
       </c>
       <c r="AI10" s="63"/>
       <c r="AJ10" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AK10" s="75" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="AL10" s="75">
         <v>5</v>
@@ -5262,14 +5674,14 @@
         <v>9</v>
       </c>
       <c r="AN10" s="75" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="AO10" s="63"/>
       <c r="AP10" s="63"/>
     </row>
     <row r="11" spans="2:42" ht="50.25">
       <c r="C11" s="104" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="D11" s="105">
         <f>D10+E10</f>
@@ -5277,10 +5689,10 @@
       </c>
       <c r="E11" s="104"/>
       <c r="AE11" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF11" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG11" s="97">
         <v>46086</v>
@@ -5299,10 +5711,10 @@
     </row>
     <row r="12" spans="2:42" ht="50.25">
       <c r="AE12" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF12" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG12" s="96">
         <v>46152</v>
@@ -5321,10 +5733,10 @@
     </row>
     <row r="13" spans="2:42" ht="50.25">
       <c r="AE13" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF13" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG13" s="97">
         <v>46315</v>
@@ -5343,13 +5755,13 @@
     </row>
     <row r="14" spans="2:42" ht="50.25">
       <c r="AE14" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF14" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG14" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH14" s="75">
         <v>0</v>
@@ -5365,13 +5777,13 @@
     </row>
     <row r="15" spans="2:42" ht="50.25">
       <c r="AE15" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF15" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG15" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH15" s="71">
         <v>0</v>
@@ -5387,13 +5799,13 @@
     </row>
     <row r="16" spans="2:42" ht="50.25">
       <c r="AE16" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF16" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG16" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH16" s="75">
         <v>8</v>
@@ -5409,13 +5821,13 @@
     </row>
     <row r="17" spans="31:42" ht="50.25">
       <c r="AE17" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF17" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG17" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH17" s="71">
         <v>3</v>
@@ -5431,10 +5843,10 @@
     </row>
     <row r="18" spans="31:42" ht="50.25">
       <c r="AE18" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF18" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG18" s="96">
         <v>46086</v>
@@ -5453,10 +5865,10 @@
     </row>
     <row r="19" spans="31:42" ht="50.25">
       <c r="AE19" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF19" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG19" s="97">
         <v>46152</v>
@@ -5475,10 +5887,10 @@
     </row>
     <row r="20" spans="31:42" ht="50.25">
       <c r="AE20" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF20" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG20" s="96">
         <v>46315</v>
@@ -5497,13 +5909,13 @@
     </row>
     <row r="21" spans="31:42" ht="50.25">
       <c r="AE21" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF21" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG21" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH21" s="71">
         <v>1</v>
@@ -5519,13 +5931,13 @@
     </row>
     <row r="22" spans="31:42" ht="50.25">
       <c r="AE22" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF22" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG22" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH22" s="75">
         <v>1</v>
@@ -5541,13 +5953,13 @@
     </row>
     <row r="23" spans="31:42" ht="50.25">
       <c r="AE23" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF23" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG23" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH23" s="71">
         <v>5</v>
@@ -5563,13 +5975,13 @@
     </row>
     <row r="24" spans="31:42" ht="66.75">
       <c r="AE24" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF24" s="75" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG24" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH24" s="75">
         <v>1</v>
@@ -5585,10 +5997,10 @@
     </row>
     <row r="25" spans="31:42" ht="66.75">
       <c r="AE25" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF25" s="71" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG25" s="97">
         <v>46086</v>
@@ -5607,10 +6019,10 @@
     </row>
     <row r="26" spans="31:42" ht="66.75">
       <c r="AE26" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF26" s="75" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG26" s="96">
         <v>46152</v>
@@ -5629,10 +6041,10 @@
     </row>
     <row r="27" spans="31:42" ht="66.75">
       <c r="AE27" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF27" s="71" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG27" s="97">
         <v>46315</v>
@@ -5651,13 +6063,13 @@
     </row>
     <row r="28" spans="31:42" ht="66.75">
       <c r="AE28" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF28" s="75" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG28" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH28" s="75">
         <v>0</v>
@@ -5673,13 +6085,13 @@
     </row>
     <row r="29" spans="31:42" ht="66.75">
       <c r="AE29" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF29" s="71" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG29" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH29" s="71">
         <v>0</v>
@@ -5695,13 +6107,13 @@
     </row>
     <row r="30" spans="31:42" ht="66.75">
       <c r="AE30" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF30" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG30" s="75" t="s">
         <v>93</v>
-      </c>
-      <c r="AG30" s="75" t="s">
-        <v>54</v>
       </c>
       <c r="AH30" s="75">
         <v>3</v>
@@ -5717,13 +6129,13 @@
     </row>
     <row r="31" spans="31:42" ht="66.75">
       <c r="AE31" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF31" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG31" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH31" s="71">
         <v>3</v>
@@ -5739,10 +6151,10 @@
     </row>
     <row r="32" spans="31:42" ht="66.75">
       <c r="AE32" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF32" s="75" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG32" s="96">
         <v>46086</v>
@@ -5761,10 +6173,10 @@
     </row>
     <row r="33" spans="31:42" ht="66.75">
       <c r="AE33" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF33" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG33" s="97">
         <v>46152</v>
@@ -5783,10 +6195,10 @@
     </row>
     <row r="34" spans="31:42" ht="66.75">
       <c r="AE34" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF34" s="75" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG34" s="96">
         <v>46315</v>
@@ -5805,13 +6217,13 @@
     </row>
     <row r="35" spans="31:42" ht="66.75">
       <c r="AE35" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF35" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG35" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH35" s="71">
         <v>0</v>
@@ -5827,13 +6239,13 @@
     </row>
     <row r="36" spans="31:42" ht="66.75">
       <c r="AE36" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF36" s="75" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG36" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH36" s="75">
         <v>0</v>
@@ -5849,13 +6261,13 @@
     </row>
     <row r="37" spans="31:42" ht="66.75">
       <c r="AE37" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF37" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG37" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH37" s="71">
         <v>3</v>
@@ -5871,13 +6283,13 @@
     </row>
     <row r="38" spans="31:42" ht="33.75">
       <c r="AE38" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF38" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG38" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH38" s="75">
         <v>2</v>
@@ -5893,10 +6305,10 @@
     </row>
     <row r="39" spans="31:42" ht="33.75">
       <c r="AE39" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF39" s="71" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG39" s="97">
         <v>46086</v>
@@ -5915,10 +6327,10 @@
     </row>
     <row r="40" spans="31:42" ht="33.75">
       <c r="AE40" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF40" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG40" s="96">
         <v>46152</v>
@@ -5937,10 +6349,10 @@
     </row>
     <row r="41" spans="31:42" ht="33.75">
       <c r="AE41" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF41" s="71" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG41" s="97">
         <v>46315</v>
@@ -5959,13 +6371,13 @@
     </row>
     <row r="42" spans="31:42" ht="33.75">
       <c r="AE42" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF42" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG42" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH42" s="75">
         <v>0</v>
@@ -5981,13 +6393,13 @@
     </row>
     <row r="43" spans="31:42" ht="33.75">
       <c r="AE43" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF43" s="71" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG43" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH43" s="71">
         <v>0</v>
@@ -6003,13 +6415,13 @@
     </row>
     <row r="44" spans="31:42" ht="33.75">
       <c r="AE44" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF44" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG44" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH44" s="75">
         <v>2</v>
@@ -6025,13 +6437,13 @@
     </row>
     <row r="45" spans="31:42" ht="50.25">
       <c r="AE45" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF45" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG45" s="71" t="s">
         <v>96</v>
-      </c>
-      <c r="AG45" s="71" t="s">
-        <v>57</v>
       </c>
       <c r="AH45" s="71">
         <v>1</v>
@@ -6047,10 +6459,10 @@
     </row>
     <row r="46" spans="31:42" ht="50.25">
       <c r="AE46" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF46" s="75" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG46" s="96">
         <v>46086</v>
@@ -6069,10 +6481,10 @@
     </row>
     <row r="47" spans="31:42" ht="50.25">
       <c r="AE47" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF47" s="71" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG47" s="97">
         <v>46152</v>
@@ -6091,10 +6503,10 @@
     </row>
     <row r="48" spans="31:42" ht="50.25">
       <c r="AE48" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF48" s="75" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG48" s="96">
         <v>46315</v>
@@ -6113,13 +6525,13 @@
     </row>
     <row r="49" spans="31:42" ht="50.25">
       <c r="AE49" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF49" s="71" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG49" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH49" s="71">
         <v>0</v>
@@ -6135,13 +6547,13 @@
     </row>
     <row r="50" spans="31:42" ht="50.25">
       <c r="AE50" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF50" s="75" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG50" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH50" s="75">
         <v>0</v>
@@ -6157,13 +6569,13 @@
     </row>
     <row r="51" spans="31:42" ht="50.25">
       <c r="AE51" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF51" s="71" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG51" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH51" s="71">
         <v>1</v>
@@ -6179,13 +6591,13 @@
     </row>
     <row r="52" spans="31:42" ht="50.25">
       <c r="AE52" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF52" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG52" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH52" s="75">
         <v>1</v>
@@ -6201,10 +6613,10 @@
     </row>
     <row r="53" spans="31:42" ht="50.25">
       <c r="AE53" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF53" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG53" s="97">
         <v>46086</v>
@@ -6223,10 +6635,10 @@
     </row>
     <row r="54" spans="31:42" ht="50.25">
       <c r="AE54" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF54" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG54" s="96">
         <v>46152</v>
@@ -6245,10 +6657,10 @@
     </row>
     <row r="55" spans="31:42" ht="50.25">
       <c r="AE55" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF55" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG55" s="97">
         <v>46315</v>
@@ -6267,13 +6679,13 @@
     </row>
     <row r="56" spans="31:42" ht="50.25">
       <c r="AE56" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF56" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG56" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH56" s="75">
         <v>0</v>
@@ -6289,13 +6701,13 @@
     </row>
     <row r="57" spans="31:42" ht="50.25">
       <c r="AE57" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF57" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG57" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH57" s="71">
         <v>0</v>
@@ -6311,13 +6723,13 @@
     </row>
     <row r="58" spans="31:42" ht="50.25">
       <c r="AE58" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF58" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG58" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH58" s="75">
         <v>1</v>
@@ -6333,13 +6745,13 @@
     </row>
     <row r="59" spans="31:42" ht="33.75">
       <c r="AE59" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF59" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG59" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH59" s="71">
         <v>0</v>
@@ -6355,10 +6767,10 @@
     </row>
     <row r="60" spans="31:42" ht="33.75">
       <c r="AE60" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF60" s="75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG60" s="96">
         <v>46086</v>
@@ -6377,10 +6789,10 @@
     </row>
     <row r="61" spans="31:42" ht="33.75">
       <c r="AE61" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF61" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG61" s="97">
         <v>46152</v>
@@ -6399,10 +6811,10 @@
     </row>
     <row r="62" spans="31:42" ht="33.75">
       <c r="AE62" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF62" s="75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG62" s="96">
         <v>46315</v>
@@ -6421,13 +6833,13 @@
     </row>
     <row r="63" spans="31:42" ht="33.75">
       <c r="AE63" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF63" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG63" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH63" s="71">
         <v>0</v>
@@ -6443,13 +6855,13 @@
     </row>
     <row r="64" spans="31:42" ht="33.75">
       <c r="AE64" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF64" s="75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG64" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH64" s="75">
         <v>0</v>
@@ -6465,13 +6877,13 @@
     </row>
     <row r="65" spans="31:42" ht="33.75">
       <c r="AE65" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF65" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG65" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH65" s="71">
         <v>1</v>
@@ -6487,13 +6899,13 @@
     </row>
     <row r="66" spans="31:42" ht="33.75">
       <c r="AE66" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF66" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG66" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH66" s="75">
         <v>27</v>
@@ -6509,10 +6921,10 @@
     </row>
     <row r="67" spans="31:42" ht="33.75">
       <c r="AE67" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF67" s="71" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG67" s="97">
         <v>46086</v>
@@ -6531,10 +6943,10 @@
     </row>
     <row r="68" spans="31:42" ht="33.75">
       <c r="AE68" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF68" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG68" s="96">
         <v>46152</v>
@@ -6553,10 +6965,10 @@
     </row>
     <row r="69" spans="31:42" ht="33.75">
       <c r="AE69" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF69" s="71" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG69" s="97">
         <v>46315</v>
@@ -6575,13 +6987,13 @@
     </row>
     <row r="70" spans="31:42" ht="33.75">
       <c r="AE70" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF70" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG70" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH70" s="75">
         <v>1</v>
@@ -6597,13 +7009,13 @@
     </row>
     <row r="71" spans="31:42" ht="33.75">
       <c r="AE71" s="70" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF71" s="71" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG71" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH71" s="71">
         <v>1</v>
@@ -6619,13 +7031,13 @@
     </row>
     <row r="72" spans="31:42" ht="33.75">
       <c r="AE72" s="74" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="AF72" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG72" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH72" s="75">
         <v>39</v>
@@ -6641,13 +7053,13 @@
     </row>
     <row r="73" spans="31:42" ht="33.75">
       <c r="AE73" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF73" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG73" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH73" s="71">
         <v>22</v>
@@ -6663,10 +7075,10 @@
     </row>
     <row r="74" spans="31:42" ht="33.75">
       <c r="AE74" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF74" s="75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG74" s="96">
         <v>46086</v>
@@ -6685,10 +7097,10 @@
     </row>
     <row r="75" spans="31:42" ht="33.75">
       <c r="AE75" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF75" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG75" s="97">
         <v>46152</v>
@@ -6707,10 +7119,10 @@
     </row>
     <row r="76" spans="31:42" ht="33.75">
       <c r="AE76" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF76" s="75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG76" s="96">
         <v>46315</v>
@@ -6729,13 +7141,13 @@
     </row>
     <row r="77" spans="31:42" ht="33.75">
       <c r="AE77" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF77" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG77" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH77" s="71">
         <v>3</v>
@@ -6751,13 +7163,13 @@
     </row>
     <row r="78" spans="31:42" ht="33.75">
       <c r="AE78" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF78" s="75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG78" s="75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH78" s="75">
         <v>3</v>
@@ -6773,13 +7185,13 @@
     </row>
     <row r="79" spans="31:42" ht="33.75">
       <c r="AE79" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF79" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG79" s="71" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH79" s="71">
         <v>1</v>
@@ -6795,13 +7207,13 @@
     </row>
     <row r="80" spans="31:42" ht="33.75">
       <c r="AE80" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF80" s="75" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG80" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH80" s="75">
         <v>15</v>
@@ -6817,13 +7229,13 @@
     </row>
     <row r="81" spans="31:42" ht="33.75">
       <c r="AE81" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF81" s="71" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AG81" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH81" s="71">
         <v>57</v>
@@ -6839,13 +7251,13 @@
     </row>
     <row r="82" spans="31:42" ht="50.25">
       <c r="AE82" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF82" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG82" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH82" s="75">
         <v>11</v>
@@ -6861,10 +7273,10 @@
     </row>
     <row r="83" spans="31:42" ht="50.25">
       <c r="AE83" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF83" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG83" s="97">
         <v>46086</v>
@@ -6883,10 +7295,10 @@
     </row>
     <row r="84" spans="31:42" ht="50.25">
       <c r="AE84" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF84" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG84" s="96">
         <v>46152</v>
@@ -6905,10 +7317,10 @@
     </row>
     <row r="85" spans="31:42" ht="50.25">
       <c r="AE85" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF85" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG85" s="97">
         <v>46315</v>
@@ -6927,13 +7339,13 @@
     </row>
     <row r="86" spans="31:42" ht="50.25">
       <c r="AE86" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF86" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG86" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH86" s="75">
         <v>8</v>
@@ -6949,13 +7361,13 @@
     </row>
     <row r="87" spans="31:42" ht="50.25">
       <c r="AE87" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF87" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG87" s="71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH87" s="71">
         <v>5</v>
@@ -6971,13 +7383,13 @@
     </row>
     <row r="88" spans="31:42" ht="50.25">
       <c r="AE88" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF88" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG88" s="75" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH88" s="75">
         <v>0</v>
@@ -6993,13 +7405,13 @@
     </row>
     <row r="89" spans="31:42" ht="50.25">
       <c r="AE89" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF89" s="71" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG89" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH89" s="71">
         <v>0</v>
@@ -7015,13 +7427,13 @@
     </row>
     <row r="90" spans="31:42" ht="50.25">
       <c r="AE90" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF90" s="75" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="AG90" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH90" s="75">
         <v>36</v>
@@ -7037,13 +7449,13 @@
     </row>
     <row r="91" spans="31:42" ht="50.25">
       <c r="AE91" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF91" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG91" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH91" s="71">
         <v>5</v>
@@ -7059,10 +7471,10 @@
     </row>
     <row r="92" spans="31:42" ht="50.25">
       <c r="AE92" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF92" s="75" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG92" s="96">
         <v>46086</v>
@@ -7081,10 +7493,10 @@
     </row>
     <row r="93" spans="31:42" ht="50.25">
       <c r="AE93" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF93" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG93" s="97">
         <v>46152</v>
@@ -7103,10 +7515,10 @@
     </row>
     <row r="94" spans="31:42" ht="50.25">
       <c r="AE94" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF94" s="75" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG94" s="96">
         <v>46315</v>
@@ -7125,13 +7537,13 @@
     </row>
     <row r="95" spans="31:42" ht="50.25">
       <c r="AE95" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF95" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG95" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH95" s="71">
         <v>3</v>
@@ -7147,13 +7559,13 @@
     </row>
     <row r="96" spans="31:42" ht="50.25">
       <c r="AE96" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF96" s="75" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG96" s="75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH96" s="75">
         <v>1</v>
@@ -7169,13 +7581,13 @@
     </row>
     <row r="97" spans="31:42" ht="50.25">
       <c r="AE97" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF97" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG97" s="71" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH97" s="71">
         <v>0</v>
@@ -7191,13 +7603,13 @@
     </row>
     <row r="98" spans="31:42" ht="50.25">
       <c r="AE98" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF98" s="75" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG98" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH98" s="75">
         <v>0</v>
@@ -7213,13 +7625,13 @@
     </row>
     <row r="99" spans="31:42" ht="50.25">
       <c r="AE99" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF99" s="71" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AG99" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH99" s="71">
         <v>22</v>
@@ -7235,13 +7647,13 @@
     </row>
     <row r="100" spans="31:42" ht="50.25">
       <c r="AE100" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF100" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG100" s="75" t="s">
         <v>96</v>
-      </c>
-      <c r="AG100" s="75" t="s">
-        <v>57</v>
       </c>
       <c r="AH100" s="75">
         <v>12</v>
@@ -7257,10 +7669,10 @@
     </row>
     <row r="101" spans="31:42" ht="50.25">
       <c r="AE101" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF101" s="71" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG101" s="97">
         <v>46086</v>
@@ -7279,10 +7691,10 @@
     </row>
     <row r="102" spans="31:42" ht="50.25">
       <c r="AE102" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF102" s="75" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG102" s="96">
         <v>46152</v>
@@ -7301,10 +7713,10 @@
     </row>
     <row r="103" spans="31:42" ht="50.25">
       <c r="AE103" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF103" s="71" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG103" s="97">
         <v>46315</v>
@@ -7323,13 +7735,13 @@
     </row>
     <row r="104" spans="31:42" ht="50.25">
       <c r="AE104" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF104" s="75" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG104" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH104" s="75">
         <v>0</v>
@@ -7345,13 +7757,13 @@
     </row>
     <row r="105" spans="31:42" ht="50.25">
       <c r="AE105" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF105" s="71" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG105" s="71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH105" s="71">
         <v>0</v>
@@ -7367,13 +7779,13 @@
     </row>
     <row r="106" spans="31:42" ht="50.25">
       <c r="AE106" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF106" s="75" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG106" s="75" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH106" s="75">
         <v>0</v>
@@ -7389,13 +7801,13 @@
     </row>
     <row r="107" spans="31:42" ht="50.25">
       <c r="AE107" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF107" s="71" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG107" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH107" s="71">
         <v>0</v>
@@ -7411,13 +7823,13 @@
     </row>
     <row r="108" spans="31:42" ht="50.25">
       <c r="AE108" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF108" s="75" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="AG108" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH108" s="75">
         <v>15</v>
@@ -7433,13 +7845,13 @@
     </row>
     <row r="109" spans="31:42" ht="66.75">
       <c r="AE109" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF109" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG109" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH109" s="71">
         <v>7</v>
@@ -7455,10 +7867,10 @@
     </row>
     <row r="110" spans="31:42" ht="66.75">
       <c r="AE110" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF110" s="75" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG110" s="96">
         <v>46086</v>
@@ -7477,10 +7889,10 @@
     </row>
     <row r="111" spans="31:42" ht="66.75">
       <c r="AE111" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF111" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG111" s="97">
         <v>46152</v>
@@ -7499,10 +7911,10 @@
     </row>
     <row r="112" spans="31:42" ht="66.75">
       <c r="AE112" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF112" s="75" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG112" s="96">
         <v>46315</v>
@@ -7521,13 +7933,13 @@
     </row>
     <row r="113" spans="31:42" ht="66.75">
       <c r="AE113" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF113" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG113" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH113" s="71">
         <v>0</v>
@@ -7543,13 +7955,13 @@
     </row>
     <row r="114" spans="31:42" ht="66.75">
       <c r="AE114" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF114" s="75" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG114" s="75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH114" s="75">
         <v>0</v>
@@ -7565,13 +7977,13 @@
     </row>
     <row r="115" spans="31:42" ht="66.75">
       <c r="AE115" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF115" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG115" s="71" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH115" s="71">
         <v>0</v>
@@ -7587,13 +7999,13 @@
     </row>
     <row r="116" spans="31:42" ht="66.75">
       <c r="AE116" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF116" s="75" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG116" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH116" s="75">
         <v>0</v>
@@ -7609,13 +8021,13 @@
     </row>
     <row r="117" spans="31:42" ht="66.75">
       <c r="AE117" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF117" s="71" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AG117" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH117" s="71">
         <v>12</v>
@@ -7631,13 +8043,13 @@
     </row>
     <row r="118" spans="31:42" ht="33.75">
       <c r="AE118" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF118" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG118" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH118" s="75">
         <v>6</v>
@@ -7653,10 +8065,10 @@
     </row>
     <row r="119" spans="31:42" ht="33.75">
       <c r="AE119" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF119" s="71" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG119" s="97">
         <v>46086</v>
@@ -7675,10 +8087,10 @@
     </row>
     <row r="120" spans="31:42" ht="33.75">
       <c r="AE120" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF120" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG120" s="96">
         <v>46152</v>
@@ -7697,10 +8109,10 @@
     </row>
     <row r="121" spans="31:42" ht="33.75">
       <c r="AE121" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF121" s="71" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG121" s="97">
         <v>46315</v>
@@ -7719,13 +8131,13 @@
     </row>
     <row r="122" spans="31:42" ht="33.75">
       <c r="AE122" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF122" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG122" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH122" s="75">
         <v>0</v>
@@ -7741,13 +8153,13 @@
     </row>
     <row r="123" spans="31:42" ht="33.75">
       <c r="AE123" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF123" s="71" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG123" s="71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH123" s="71">
         <v>0</v>
@@ -7763,13 +8175,13 @@
     </row>
     <row r="124" spans="31:42" ht="33.75">
       <c r="AE124" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF124" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG124" s="75" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH124" s="75">
         <v>0</v>
@@ -7785,13 +8197,13 @@
     </row>
     <row r="125" spans="31:42" ht="33.75">
       <c r="AE125" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF125" s="71" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG125" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH125" s="71">
         <v>0</v>
@@ -7807,13 +8219,13 @@
     </row>
     <row r="126" spans="31:42" ht="33.75">
       <c r="AE126" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF126" s="75" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="AG126" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH126" s="75">
         <v>10</v>
@@ -7829,13 +8241,13 @@
     </row>
     <row r="127" spans="31:42" ht="50.25">
       <c r="AE127" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF127" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG127" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH127" s="71">
         <v>6</v>
@@ -7851,10 +8263,10 @@
     </row>
     <row r="128" spans="31:42" ht="50.25">
       <c r="AE128" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF128" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG128" s="96">
         <v>46086</v>
@@ -7873,10 +8285,10 @@
     </row>
     <row r="129" spans="31:42" ht="50.25">
       <c r="AE129" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF129" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG129" s="97">
         <v>46152</v>
@@ -7895,10 +8307,10 @@
     </row>
     <row r="130" spans="31:42" ht="50.25">
       <c r="AE130" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF130" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG130" s="96">
         <v>46315</v>
@@ -7917,13 +8329,13 @@
     </row>
     <row r="131" spans="31:42" ht="50.25">
       <c r="AE131" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF131" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG131" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH131" s="71">
         <v>0</v>
@@ -7939,13 +8351,13 @@
     </row>
     <row r="132" spans="31:42" ht="50.25">
       <c r="AE132" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF132" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG132" s="75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH132" s="75">
         <v>0</v>
@@ -7961,13 +8373,13 @@
     </row>
     <row r="133" spans="31:42" ht="50.25">
       <c r="AE133" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF133" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG133" s="71" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH133" s="71">
         <v>0</v>
@@ -7983,13 +8395,13 @@
     </row>
     <row r="134" spans="31:42" ht="50.25">
       <c r="AE134" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF134" s="75" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG134" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH134" s="75">
         <v>0</v>
@@ -8005,13 +8417,13 @@
     </row>
     <row r="135" spans="31:42" ht="50.25">
       <c r="AE135" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF135" s="71" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="AG135" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH135" s="71">
         <v>6</v>
@@ -8027,13 +8439,13 @@
     </row>
     <row r="136" spans="31:42" ht="66.75">
       <c r="AE136" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF136" s="75" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG136" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH136" s="75">
         <v>3</v>
@@ -8049,10 +8461,10 @@
     </row>
     <row r="137" spans="31:42" ht="66.75">
       <c r="AE137" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF137" s="71" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG137" s="97">
         <v>46086</v>
@@ -8071,10 +8483,10 @@
     </row>
     <row r="138" spans="31:42" ht="66.75">
       <c r="AE138" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF138" s="75" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG138" s="96">
         <v>46152</v>
@@ -8093,10 +8505,10 @@
     </row>
     <row r="139" spans="31:42" ht="66.75">
       <c r="AE139" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF139" s="71" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG139" s="97">
         <v>46315</v>
@@ -8115,13 +8527,13 @@
     </row>
     <row r="140" spans="31:42" ht="66.75">
       <c r="AE140" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF140" s="75" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG140" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH140" s="75">
         <v>0</v>
@@ -8137,13 +8549,13 @@
     </row>
     <row r="141" spans="31:42" ht="66.75">
       <c r="AE141" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF141" s="71" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG141" s="71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH141" s="71">
         <v>0</v>
@@ -8159,13 +8571,13 @@
     </row>
     <row r="142" spans="31:42" ht="66.75">
       <c r="AE142" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF142" s="75" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG142" s="75" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH142" s="75">
         <v>0</v>
@@ -8181,13 +8593,13 @@
     </row>
     <row r="143" spans="31:42" ht="66.75">
       <c r="AE143" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF143" s="71" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="AG143" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH143" s="71">
         <v>0</v>
@@ -8203,13 +8615,13 @@
     </row>
     <row r="144" spans="31:42" ht="66.75">
       <c r="AE144" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF144" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG144" s="75" t="s">
         <v>93</v>
-      </c>
-      <c r="AG144" s="75" t="s">
-        <v>54</v>
       </c>
       <c r="AH144" s="75">
         <v>5</v>
@@ -8225,13 +8637,13 @@
     </row>
     <row r="145" spans="31:42" ht="84">
       <c r="AE145" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF145" s="71" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG145" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH145" s="71">
         <v>2</v>
@@ -8247,10 +8659,10 @@
     </row>
     <row r="146" spans="31:42" ht="84">
       <c r="AE146" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF146" s="75" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG146" s="96">
         <v>46086</v>
@@ -8269,10 +8681,10 @@
     </row>
     <row r="147" spans="31:42" ht="84">
       <c r="AE147" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF147" s="71" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG147" s="97">
         <v>46152</v>
@@ -8291,10 +8703,10 @@
     </row>
     <row r="148" spans="31:42" ht="84">
       <c r="AE148" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF148" s="75" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG148" s="96">
         <v>46315</v>
@@ -8313,13 +8725,13 @@
     </row>
     <row r="149" spans="31:42" ht="84">
       <c r="AE149" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF149" s="71" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG149" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH149" s="71">
         <v>0</v>
@@ -8335,13 +8747,13 @@
     </row>
     <row r="150" spans="31:42" ht="84">
       <c r="AE150" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF150" s="75" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG150" s="75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH150" s="75">
         <v>0</v>
@@ -8357,13 +8769,13 @@
     </row>
     <row r="151" spans="31:42" ht="84">
       <c r="AE151" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF151" s="71" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG151" s="71" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH151" s="71">
         <v>0</v>
@@ -8379,13 +8791,13 @@
     </row>
     <row r="152" spans="31:42" ht="84">
       <c r="AE152" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF152" s="75" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG152" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH152" s="75">
         <v>0</v>
@@ -8401,13 +8813,13 @@
     </row>
     <row r="153" spans="31:42" ht="84">
       <c r="AE153" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF153" s="71" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AG153" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH153" s="71">
         <v>4</v>
@@ -8423,13 +8835,13 @@
     </row>
     <row r="154" spans="31:42" ht="33.75">
       <c r="AE154" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF154" s="75" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG154" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH154" s="75">
         <v>3</v>
@@ -8445,10 +8857,10 @@
     </row>
     <row r="155" spans="31:42" ht="33.75">
       <c r="AE155" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF155" s="71" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG155" s="97">
         <v>46086</v>
@@ -8467,10 +8879,10 @@
     </row>
     <row r="156" spans="31:42" ht="33.75">
       <c r="AE156" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF156" s="75" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG156" s="96">
         <v>46152</v>
@@ -8489,10 +8901,10 @@
     </row>
     <row r="157" spans="31:42" ht="33.75">
       <c r="AE157" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF157" s="71" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG157" s="97">
         <v>46315</v>
@@ -8511,13 +8923,13 @@
     </row>
     <row r="158" spans="31:42" ht="33.75">
       <c r="AE158" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF158" s="75" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG158" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH158" s="75">
         <v>0</v>
@@ -8533,13 +8945,13 @@
     </row>
     <row r="159" spans="31:42" ht="33.75">
       <c r="AE159" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF159" s="71" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG159" s="71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH159" s="71">
         <v>1</v>
@@ -8555,13 +8967,13 @@
     </row>
     <row r="160" spans="31:42" ht="33.75">
       <c r="AE160" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF160" s="75" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG160" s="75" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH160" s="75">
         <v>0</v>
@@ -8577,13 +8989,13 @@
     </row>
     <row r="161" spans="31:42" ht="33.75">
       <c r="AE161" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF161" s="71" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG161" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH161" s="71">
         <v>0</v>
@@ -8599,13 +9011,13 @@
     </row>
     <row r="162" spans="31:42" ht="33.75">
       <c r="AE162" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF162" s="75" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AG162" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH162" s="75">
         <v>4</v>
@@ -8621,13 +9033,13 @@
     </row>
     <row r="163" spans="31:42" ht="50.25">
       <c r="AE163" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF163" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG163" s="71" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH163" s="71">
         <v>2</v>
@@ -8643,10 +9055,10 @@
     </row>
     <row r="164" spans="31:42" ht="50.25">
       <c r="AE164" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF164" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG164" s="96">
         <v>46086</v>
@@ -8665,10 +9077,10 @@
     </row>
     <row r="165" spans="31:42" ht="50.25">
       <c r="AE165" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF165" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG165" s="97">
         <v>46152</v>
@@ -8687,10 +9099,10 @@
     </row>
     <row r="166" spans="31:42" ht="50.25">
       <c r="AE166" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF166" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG166" s="96">
         <v>46315</v>
@@ -8709,13 +9121,13 @@
     </row>
     <row r="167" spans="31:42" ht="50.25">
       <c r="AE167" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF167" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG167" s="71" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH167" s="71">
         <v>0</v>
@@ -8731,13 +9143,13 @@
     </row>
     <row r="168" spans="31:42" ht="50.25">
       <c r="AE168" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF168" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG168" s="75" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH168" s="75">
         <v>0</v>
@@ -8753,13 +9165,13 @@
     </row>
     <row r="169" spans="31:42" ht="50.25">
       <c r="AE169" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF169" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG169" s="71" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH169" s="71">
         <v>0</v>
@@ -8775,13 +9187,13 @@
     </row>
     <row r="170" spans="31:42" ht="50.25">
       <c r="AE170" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF170" s="75" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG170" s="75" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH170" s="75">
         <v>0</v>
@@ -8797,13 +9209,13 @@
     </row>
     <row r="171" spans="31:42" ht="50.25">
       <c r="AE171" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF171" s="71" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AG171" s="71" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH171" s="71">
         <v>3</v>
@@ -8819,13 +9231,13 @@
     </row>
     <row r="172" spans="31:42" ht="33.75">
       <c r="AE172" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF172" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG172" s="75" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="AH172" s="75">
         <v>79</v>
@@ -8841,10 +9253,10 @@
     </row>
     <row r="173" spans="31:42" ht="33.75">
       <c r="AE173" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF173" s="71" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG173" s="97">
         <v>46086</v>
@@ -8863,10 +9275,10 @@
     </row>
     <row r="174" spans="31:42" ht="33.75">
       <c r="AE174" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF174" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG174" s="96">
         <v>46152</v>
@@ -8885,10 +9297,10 @@
     </row>
     <row r="175" spans="31:42" ht="33.75">
       <c r="AE175" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF175" s="71" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG175" s="97">
         <v>46315</v>
@@ -8907,13 +9319,13 @@
     </row>
     <row r="176" spans="31:42" ht="33.75">
       <c r="AE176" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF176" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG176" s="75" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AH176" s="75">
         <v>14</v>
@@ -8929,13 +9341,13 @@
     </row>
     <row r="177" spans="31:42" ht="33.75">
       <c r="AE177" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF177" s="71" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG177" s="71" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AH177" s="71">
         <v>10</v>
@@ -8951,13 +9363,13 @@
     </row>
     <row r="178" spans="31:42" ht="33.75">
       <c r="AE178" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF178" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG178" s="75" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AH178" s="75">
         <v>1</v>
@@ -8973,13 +9385,13 @@
     </row>
     <row r="179" spans="31:42" ht="33.75">
       <c r="AE179" s="70" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF179" s="71" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG179" s="71" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="AH179" s="71">
         <v>15</v>
@@ -8995,13 +9407,13 @@
     </row>
     <row r="180" spans="31:42" ht="33.75">
       <c r="AE180" s="74" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="AF180" s="75" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="AG180" s="75" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="AH180" s="75">
         <v>174</v>
@@ -9017,17 +9429,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="G4:G8"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="L4:L8"/>
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AJ1:AN1"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="Q4:Q8"/>
     <mergeCell ref="W2:AC2"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G4:G8"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="L4:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9057,17 +9469,17 @@
   <sheetData>
     <row r="2" spans="3:39">
       <c r="C2" s="120" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="D2" s="120"/>
       <c r="G2" s="120" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H2" s="120"/>
       <c r="I2" s="120"/>
       <c r="J2" s="120"/>
       <c r="M2" s="120" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="N2" s="120"/>
       <c r="O2" s="120"/>
@@ -9075,12 +9487,12 @@
       <c r="Q2" s="120"/>
       <c r="R2" s="120"/>
       <c r="U2" s="120" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="V2" s="120"/>
       <c r="W2" s="120"/>
       <c r="AF2" s="120" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AG2" s="120"/>
       <c r="AH2" s="120"/>
@@ -9092,64 +9504,64 @@
     </row>
     <row r="3" spans="3:39" ht="45.75">
       <c r="C3" s="46" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="G3" s="50" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="H3" s="50" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="J3" s="50" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="M3" s="53" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="N3" s="53" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="O3" s="53" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="P3" s="53" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="Q3" s="54" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="R3" s="53" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="U3" s="53" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="V3" s="53" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="W3" s="53" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="Z3" s="64" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="AA3" s="64" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="AB3" s="64" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="AC3" s="64" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="AF3" s="65" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="AG3" s="66">
         <f>SUM(AG4:AG6)</f>
@@ -9157,14 +9569,14 @@
       </c>
       <c r="AH3" s="63"/>
       <c r="AI3" s="65" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="AJ3" s="66">
         <v>289</v>
       </c>
       <c r="AK3" s="63"/>
       <c r="AL3" s="65" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="AM3" s="66">
         <f>AM4+AM5</f>
@@ -9173,7 +9585,7 @@
     </row>
     <row r="4" spans="3:39">
       <c r="C4" s="44" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="D4" s="44">
         <v>3613</v>
@@ -9188,10 +9600,10 @@
         <v>46387</v>
       </c>
       <c r="J4" s="49" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="M4" s="52" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="N4" s="51">
         <v>16</v>
@@ -9206,10 +9618,10 @@
         <v>11</v>
       </c>
       <c r="R4" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="T4" s="109" t="s">
-        <v>128</v>
+        <v>163</v>
+      </c>
+      <c r="T4" s="108" t="s">
+        <v>165</v>
       </c>
       <c r="U4" s="58">
         <v>46138</v>
@@ -9234,7 +9646,7 @@
         <v>56</v>
       </c>
       <c r="AF4" s="51" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="AG4" s="51">
         <v>825</v>
@@ -9244,7 +9656,7 @@
       <c r="AJ4" s="63"/>
       <c r="AK4" s="63"/>
       <c r="AL4" s="51" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="AM4" s="51">
         <v>1189</v>
@@ -9252,13 +9664,13 @@
     </row>
     <row r="5" spans="3:39">
       <c r="C5" s="44" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D5" s="44">
         <v>3084</v>
       </c>
       <c r="M5" s="52" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="N5" s="51">
         <v>16</v>
@@ -9273,9 +9685,9 @@
         <v>11</v>
       </c>
       <c r="R5" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="T5" s="109"/>
+        <v>163</v>
+      </c>
+      <c r="T5" s="108"/>
       <c r="U5" s="58">
         <v>46168</v>
       </c>
@@ -9286,7 +9698,7 @@
         <v>978</v>
       </c>
       <c r="AF5" s="51" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="AG5" s="51">
         <v>335</v>
@@ -9296,7 +9708,7 @@
       <c r="AJ5" s="63"/>
       <c r="AK5" s="63"/>
       <c r="AL5" s="51" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="AM5" s="51">
         <v>1543</v>
@@ -9304,13 +9716,13 @@
     </row>
     <row r="6" spans="3:39">
       <c r="C6" s="44" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="D6" s="44">
         <v>1265</v>
       </c>
       <c r="M6" s="55" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="N6" s="56">
         <f>SUM(N4:N5)</f>
@@ -9329,9 +9741,9 @@
         <v>22</v>
       </c>
       <c r="R6" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="T6" s="109"/>
+        <v>163</v>
+      </c>
+      <c r="T6" s="108"/>
       <c r="U6" s="58">
         <v>46199</v>
       </c>
@@ -9342,7 +9754,7 @@
         <v>1028</v>
       </c>
       <c r="AF6" s="51" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="AG6" s="51">
         <v>151</v>
@@ -9356,12 +9768,12 @@
     </row>
     <row r="7" spans="3:39">
       <c r="C7" s="44" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="D7" s="44">
         <v>49</v>
       </c>
-      <c r="T7" s="109"/>
+      <c r="T7" s="108"/>
       <c r="U7" s="58">
         <v>46229</v>
       </c>
@@ -9374,13 +9786,13 @@
     </row>
     <row r="8" spans="3:39">
       <c r="C8" s="45" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="D8" s="45">
         <f>SUM(D4:D7)</f>
         <v>8011</v>
       </c>
-      <c r="T8" s="109"/>
+      <c r="T8" s="108"/>
       <c r="U8" s="59">
         <v>46260</v>
       </c>
@@ -9392,7 +9804,7 @@
       </c>
     </row>
     <row r="9" spans="3:39">
-      <c r="T9" s="109"/>
+      <c r="T9" s="108"/>
       <c r="U9" s="59">
         <v>46291</v>
       </c>
@@ -9404,7 +9816,7 @@
       </c>
     </row>
     <row r="10" spans="3:39">
-      <c r="T10" s="109"/>
+      <c r="T10" s="108"/>
       <c r="U10" s="58">
         <v>46321</v>
       </c>
@@ -9416,7 +9828,7 @@
       </c>
     </row>
     <row r="11" spans="3:39">
-      <c r="T11" s="109"/>
+      <c r="T11" s="108"/>
       <c r="U11" s="58">
         <v>46352</v>
       </c>
@@ -9428,7 +9840,7 @@
       </c>
     </row>
     <row r="12" spans="3:39">
-      <c r="T12" s="109"/>
+      <c r="T12" s="108"/>
       <c r="U12" s="60">
         <v>46382</v>
       </c>
@@ -9441,7 +9853,7 @@
     </row>
     <row r="13" spans="3:39">
       <c r="U13" s="43" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="V13" s="43">
         <f>SUM(W4:W12)</f>
@@ -9450,7 +9862,7 @@
     </row>
     <row r="14" spans="3:39">
       <c r="U14" s="43" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="V14" s="43">
         <f>SUM(V4:V12)</f>
@@ -9459,7 +9871,7 @@
     </row>
     <row r="15" spans="3:39">
       <c r="U15" s="45" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="V15" s="62">
         <f>V13/(V13+V14)</f>
@@ -9509,7 +9921,7 @@
   <sheetData>
     <row r="4" spans="3:20" ht="30" customHeight="1">
       <c r="C4" s="122" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="D4" s="123"/>
       <c r="E4" s="123"/>
@@ -9519,30 +9931,30 @@
       <c r="I4" s="123"/>
       <c r="J4" s="123"/>
       <c r="N4" s="94" t="s">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="O4" s="94" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="P4" s="94" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="Q4" s="94" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="R4" s="94" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="S4" s="94" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="T4" s="94" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="3:20" ht="15.75">
       <c r="C5" s="90" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="D5" s="91">
         <v>46082</v>
@@ -9566,30 +9978,30 @@
         <v>46266</v>
       </c>
       <c r="N5" s="121" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="O5" s="121" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="P5" s="121" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="Q5" s="95" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="R5" s="95" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="S5" s="95" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="T5" s="95" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="3:20" ht="15.75">
       <c r="C6" s="90" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="D6" s="93">
         <v>108</v>
@@ -9607,28 +10019,28 @@
         <v>170</v>
       </c>
       <c r="I6" s="93" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="J6" s="52"/>
       <c r="N6" s="121"/>
       <c r="O6" s="121"/>
       <c r="P6" s="121"/>
       <c r="Q6" s="95" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="R6" s="95" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="S6" s="95" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="T6" s="95" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="3:20" ht="15.75">
       <c r="C7" s="92" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="D7" s="52">
         <v>253</v>
@@ -9646,20 +10058,20 @@
         <v>96</v>
       </c>
       <c r="I7" s="52" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="J7" s="52"/>
       <c r="N7" s="121"/>
       <c r="O7" s="121"/>
       <c r="P7" s="121"/>
       <c r="Q7" s="95" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="R7" s="95" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="S7" s="95" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="T7" s="95">
         <v>179</v>
@@ -9667,7 +10079,7 @@
     </row>
     <row r="8" spans="3:20" ht="15.75">
       <c r="C8" s="90" t="s">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="D8" s="52">
         <v>30</v>
@@ -9685,20 +10097,20 @@
         <v>164</v>
       </c>
       <c r="I8" s="52" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="J8" s="52"/>
       <c r="N8" s="121"/>
       <c r="O8" s="121"/>
       <c r="P8" s="121"/>
       <c r="Q8" s="95" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="R8" s="95">
         <v>657</v>
       </c>
       <c r="S8" s="95" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="T8" s="95">
         <v>552</v>
@@ -9709,13 +10121,13 @@
       <c r="O9" s="121"/>
       <c r="P9" s="121"/>
       <c r="Q9" s="95" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="R9" s="95">
         <v>206</v>
       </c>
       <c r="S9" s="95" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="T9" s="95">
         <v>249</v>
@@ -9725,19 +10137,19 @@
       <c r="N10" s="121"/>
       <c r="O10" s="121"/>
       <c r="P10" s="121" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="Q10" s="95" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="R10" s="95" t="s">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="S10" s="95" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="T10" s="95" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="3:20" ht="15.75">
@@ -9745,16 +10157,16 @@
       <c r="O11" s="121"/>
       <c r="P11" s="121"/>
       <c r="Q11" s="95" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="R11" s="95" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="S11" s="95" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="T11" s="95" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="3:20" ht="15.75">
@@ -9762,16 +10174,16 @@
       <c r="O12" s="121"/>
       <c r="P12" s="121"/>
       <c r="Q12" s="95" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="R12" s="95" t="s">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="S12" s="95" t="s">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="T12" s="95" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="3:20" ht="15.75">
@@ -9779,16 +10191,16 @@
       <c r="O13" s="121"/>
       <c r="P13" s="121"/>
       <c r="Q13" s="95" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="R13" s="95" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="S13" s="95" t="s">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="T13" s="95" t="s">
-        <v>178</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="3:20" ht="15.75">
@@ -9796,23 +10208,23 @@
       <c r="O14" s="121"/>
       <c r="P14" s="121"/>
       <c r="Q14" s="95" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="R14" s="95" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="S14" s="95" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="T14" s="95" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="3:20">
       <c r="N15" s="121"/>
       <c r="O15" s="121"/>
       <c r="P15" s="121" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="Q15" s="121"/>
       <c r="R15" s="121"/>
@@ -9858,19 +10270,19 @@
     <row r="20" spans="14:20" ht="15.75">
       <c r="N20" s="121"/>
       <c r="O20" s="121" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="P20" s="121" t="s">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="Q20" s="95" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="R20" s="95" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="S20" s="95" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="T20" s="95">
         <v>410</v>
@@ -9881,13 +10293,13 @@
       <c r="O21" s="121"/>
       <c r="P21" s="121"/>
       <c r="Q21" s="95" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="R21" s="95">
         <v>300</v>
       </c>
       <c r="S21" s="95" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="T21" s="95">
         <v>201</v>
@@ -9898,13 +10310,13 @@
       <c r="O22" s="121"/>
       <c r="P22" s="121"/>
       <c r="Q22" s="95" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="R22" s="95">
         <v>250</v>
       </c>
       <c r="S22" s="95" t="s">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="T22" s="95">
         <v>60</v>
@@ -9915,13 +10327,13 @@
       <c r="O23" s="121"/>
       <c r="P23" s="121"/>
       <c r="Q23" s="95" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="R23" s="95">
         <v>230</v>
       </c>
       <c r="S23" s="95" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="T23" s="95">
         <v>55</v>
@@ -9932,13 +10344,13 @@
       <c r="O24" s="121"/>
       <c r="P24" s="121"/>
       <c r="Q24" s="95" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="R24" s="95">
         <v>210</v>
       </c>
       <c r="S24" s="95" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="T24" s="95">
         <v>31</v>
@@ -9948,16 +10360,16 @@
       <c r="N25" s="121"/>
       <c r="O25" s="121"/>
       <c r="P25" s="121" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="Q25" s="95" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="R25" s="95" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="S25" s="95" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="T25" s="95">
         <v>165</v>
@@ -9968,13 +10380,13 @@
       <c r="O26" s="121"/>
       <c r="P26" s="121"/>
       <c r="Q26" s="95" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="R26" s="95" t="s">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="S26" s="95" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="T26" s="95">
         <v>98</v>
@@ -9985,13 +10397,13 @@
       <c r="O27" s="121"/>
       <c r="P27" s="121"/>
       <c r="Q27" s="95" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="R27" s="95">
         <v>650</v>
       </c>
       <c r="S27" s="95" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="T27" s="95">
         <v>90</v>
@@ -10002,13 +10414,13 @@
       <c r="O28" s="121"/>
       <c r="P28" s="121"/>
       <c r="Q28" s="95" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="R28" s="95">
         <v>480</v>
       </c>
       <c r="S28" s="95" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="T28" s="95">
         <v>85</v>
@@ -10019,13 +10431,13 @@
       <c r="O29" s="121"/>
       <c r="P29" s="121"/>
       <c r="Q29" s="95" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="R29" s="95">
         <v>310</v>
       </c>
       <c r="S29" s="95" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="T29" s="95">
         <v>30</v>
@@ -10035,7 +10447,7 @@
       <c r="N30" s="121"/>
       <c r="O30" s="121"/>
       <c r="P30" s="121" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="Q30" s="121"/>
       <c r="R30" s="121"/>
@@ -10130,140 +10542,140 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="B1" s="79" t="s">
-        <v>208</v>
-      </c>
-      <c r="D1" s="108" t="s">
-        <v>209</v>
-      </c>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
+        <v>245</v>
+      </c>
+      <c r="D1" s="119" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
       <c r="G1" s="80"/>
-      <c r="H1" s="108" t="s">
-        <v>210</v>
-      </c>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="M1" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108" t="s">
-        <v>209</v>
-      </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
+      <c r="H1" s="119" t="s">
+        <v>247</v>
+      </c>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="M1" s="119" t="s">
+        <v>248</v>
+      </c>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119" t="s">
+        <v>246</v>
+      </c>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
       <c r="R1" s="80"/>
-      <c r="S1" s="108" t="s">
-        <v>210</v>
-      </c>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="X1" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y1" s="108"/>
+      <c r="S1" s="119" t="s">
+        <v>247</v>
+      </c>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="X1" s="119" t="s">
+        <v>248</v>
+      </c>
+      <c r="Y1" s="119"/>
       <c r="Z1" s="67"/>
       <c r="AA1" s="67"/>
       <c r="AB1" s="67"/>
       <c r="AC1" s="67"/>
-      <c r="AE1" s="108" t="s">
-        <v>212</v>
-      </c>
-      <c r="AF1" s="108"/>
+      <c r="AE1" s="119" t="s">
+        <v>249</v>
+      </c>
+      <c r="AF1" s="119"/>
     </row>
     <row r="2" spans="1:32" ht="33">
       <c r="A2" s="70" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="B2" s="71">
         <v>599</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="E2" s="69" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="F2" s="69" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="G2" s="80"/>
       <c r="H2" s="68" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="I2" s="69" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="J2" s="69" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="K2" s="69" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="M2" s="68" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="N2" s="69" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="O2" s="80"/>
       <c r="P2" s="68" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="Q2" s="69" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="R2" s="69" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="T2" s="68" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="U2" s="69" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="V2" s="69" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="W2" s="69" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="X2" s="69" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="Y2" s="69" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="Z2" s="69" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="AA2" s="69" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="AB2" s="69" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="AC2" s="69" t="s">
-        <v>224</v>
+        <v>17</v>
       </c>
       <c r="AE2" s="68" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="AF2" s="69" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="117">
       <c r="A3" s="74" t="s">
-        <v>227</v>
+        <v>37</v>
       </c>
       <c r="B3" s="75">
         <v>56</v>
       </c>
       <c r="D3" s="70" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="E3" s="71">
         <v>2</v>
@@ -10273,7 +10685,7 @@
       </c>
       <c r="G3" s="80"/>
       <c r="H3" s="70" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="I3" s="71">
         <v>11</v>
@@ -10282,10 +10694,10 @@
         <v>45.83</v>
       </c>
       <c r="K3" s="71" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="M3" s="70" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="N3" s="71">
         <v>12</v>
@@ -10295,43 +10707,43 @@
         <v>46235</v>
       </c>
       <c r="Q3" s="71" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="R3" s="71">
         <v>6</v>
       </c>
       <c r="T3" s="70" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="U3" s="71" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="V3" s="71" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="W3" s="72" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="X3" s="71" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="Y3" s="71" t="s">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="Z3" s="73">
         <v>46142</v>
       </c>
       <c r="AA3" s="71" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="AB3" s="71" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="AC3" s="71" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="AE3" s="70" t="s">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="AF3" s="71">
         <v>5</v>
@@ -10339,13 +10751,13 @@
     </row>
     <row r="4" spans="1:32" ht="117">
       <c r="A4" s="70" t="s">
-        <v>242</v>
+        <v>26</v>
       </c>
       <c r="B4" s="71">
         <v>543</v>
       </c>
       <c r="D4" s="74" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="E4" s="75">
         <v>1</v>
@@ -10355,7 +10767,7 @@
       </c>
       <c r="G4" s="80"/>
       <c r="H4" s="74" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="I4" s="75">
         <v>9</v>
@@ -10364,10 +10776,10 @@
         <v>37.5</v>
       </c>
       <c r="K4" s="75" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="M4" s="74" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="N4" s="75">
         <v>9</v>
@@ -10377,43 +10789,43 @@
         <v>46235</v>
       </c>
       <c r="Q4" s="75" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="R4" s="75">
         <v>3</v>
       </c>
       <c r="T4" s="74" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="U4" s="75" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="V4" s="75" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="W4" s="76" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="X4" s="75" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="Y4" s="75" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="Z4" s="77">
         <v>46173</v>
       </c>
       <c r="AA4" s="75" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="AB4" s="75" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="AC4" s="75" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="AE4" s="74" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="AF4" s="75">
         <v>4</v>
@@ -10421,13 +10833,13 @@
     </row>
     <row r="5" spans="1:32" ht="117">
       <c r="A5" s="74" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
       <c r="B5" s="75">
         <v>0</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="E5" s="71">
         <v>1</v>
@@ -10437,7 +10849,7 @@
       </c>
       <c r="G5" s="80"/>
       <c r="H5" s="70" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="I5" s="71">
         <v>2</v>
@@ -10446,10 +10858,10 @@
         <v>8.33</v>
       </c>
       <c r="K5" s="71" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="M5" s="70" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="N5" s="71">
         <v>8</v>
@@ -10459,43 +10871,43 @@
         <v>46235</v>
       </c>
       <c r="Q5" s="71" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="R5" s="71">
         <v>1</v>
       </c>
       <c r="T5" s="70" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="U5" s="71" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="V5" s="71" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="W5" s="72" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="X5" s="71" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="Y5" s="71" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="Z5" s="73">
         <v>46173</v>
       </c>
       <c r="AA5" s="71" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="AB5" s="71" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="AC5" s="71" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="AE5" s="70" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="AF5" s="71">
         <v>1</v>
@@ -10503,7 +10915,7 @@
     </row>
     <row r="6" spans="1:32" ht="117">
       <c r="A6" s="70" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="B6" s="71">
         <v>6</v>
@@ -10513,7 +10925,7 @@
       <c r="F6" s="80"/>
       <c r="G6" s="80"/>
       <c r="H6" s="74" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="I6" s="75">
         <v>1</v>
@@ -10522,10 +10934,10 @@
         <v>4.17</v>
       </c>
       <c r="K6" s="75" t="s">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="M6" s="74" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="N6" s="75">
         <v>7</v>
@@ -10535,40 +10947,40 @@
         <v>46235</v>
       </c>
       <c r="Q6" s="75" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="R6" s="75">
         <v>1</v>
       </c>
       <c r="T6" s="74" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="U6" s="75" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="V6" s="75" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="W6" s="76" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="X6" s="75" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="Y6" s="75" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
       <c r="Z6" s="77">
         <v>46234</v>
       </c>
       <c r="AA6" s="75" t="s">
-        <v>238</v>
+        <v>273</v>
       </c>
       <c r="AB6" s="75" t="s">
-        <v>239</v>
+        <v>274</v>
       </c>
       <c r="AC6" s="75" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="183.75">
@@ -10577,34 +10989,34 @@
       <c r="F7" s="80"/>
       <c r="G7" s="80"/>
       <c r="T7" s="70" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="U7" s="71" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="V7" s="71" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="W7" s="78" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="X7" s="71" t="s">
-        <v>262</v>
+        <v>296</v>
       </c>
       <c r="Y7" s="71" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="Z7" s="73">
         <v>46249</v>
       </c>
       <c r="AA7" s="71" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
       <c r="AB7" s="71" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="AC7" s="71" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -10631,305 +11043,305 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="126" t="s">
-        <v>267</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
+      <c r="A1" s="130" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
     </row>
     <row r="2" spans="1:4" ht="33">
       <c r="A2" s="83" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
       <c r="B2" s="84" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="C2" s="84" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="D2" s="84" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="66.75">
       <c r="A3" s="85" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="C3" s="86" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="66.75">
       <c r="A4" s="87" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="B4" s="88" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="C4" s="88" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D4" s="88" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="134.25">
       <c r="A5" s="85" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="C5" s="86" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D5" s="86" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="66.75">
       <c r="A6" s="87" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="B6" s="88" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D6" s="88" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="150.75">
       <c r="A7" s="85" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="C7" s="86" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="100.5">
       <c r="A8" s="87" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="183.75">
       <c r="A9" s="85" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="C9" s="86" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="D9" s="86" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="168">
       <c r="A10" s="87" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="B10" s="88" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D10" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="66.75">
       <c r="A11" s="85" t="s">
-        <v>285</v>
+        <v>319</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="C11" s="86" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="D11" s="86" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="50.25">
       <c r="A12" s="87" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="B12" s="88" t="s">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D12" s="88" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="117">
       <c r="A13" s="85" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>290</v>
+        <v>324</v>
       </c>
       <c r="C13" s="86" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="168">
       <c r="A14" s="87" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="B14" s="88" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="100.5">
       <c r="A15" s="85" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>292</v>
+        <v>326</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="66.75">
       <c r="A16" s="87" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="B16" s="88" t="s">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="50.25">
       <c r="A17" s="85" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="C17" s="86" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D17" s="86" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="200.25">
       <c r="A18" s="87" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="B18" s="88" t="s">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="C18" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D18" s="88" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="33.75">
       <c r="A19" s="85" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="C19" s="86" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D19" s="86" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="50.25">
       <c r="A20" s="87" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="B20" s="88" t="s">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="C20" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D20" s="88" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="50.25">
       <c r="A21" s="85" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>299</v>
+        <v>333</v>
       </c>
       <c r="C21" s="86" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D21" s="86" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="66.75">
       <c r="A22" s="87" t="s">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="B22" s="88" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -10961,52 +11373,52 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="40" t="s">
-        <v>301</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="29" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="45.75">
       <c r="A5" s="30" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>305</v>
+        <v>339</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>307</v>
+        <v>341</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="26" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="37">
@@ -11027,13 +11439,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="27" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="D7" s="28" t="str">
         <f>IF($C7="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C7,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11058,13 +11470,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="27" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="D8" s="28" t="str">
         <f t="shared" ref="D8:D18" si="0">IF($C8="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C8,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11089,13 +11501,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="27" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="D9" s="28" t="str">
         <f t="shared" ref="D9:D18" si="5">IF($C9="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C9,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11120,13 +11532,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="27" t="s">
-        <v>324</v>
+        <v>358</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>325</v>
+        <v>359</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="D10" s="28" t="str">
         <f t="shared" ref="D10:D18" si="9">IF($C10="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C10,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11151,13 +11563,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="27" t="s">
-        <v>327</v>
+        <v>361</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>328</v>
+        <v>362</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="D11" s="28" t="str">
         <f t="shared" ref="D11:D18" si="13">IF($C11="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C11,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11182,13 +11594,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="27" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="D12" s="28" t="str">
         <f t="shared" ref="D12:D18" si="17">IF($C12="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C12,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11213,13 +11625,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="27" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="D13" s="28" t="str">
         <f t="shared" ref="D13:D18" si="21">IF($C13="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C13,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11244,13 +11656,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="27" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="D14" s="28" t="str">
         <f t="shared" ref="D14:D18" si="25">IF($C14="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C14,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11275,13 +11687,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="27" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>339</v>
+        <v>373</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="D15" s="28" t="str">
         <f t="shared" ref="D15:D18" si="29">IF($C15="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C15,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11306,13 +11718,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="27" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="D16" s="28" t="str">
         <f t="shared" ref="D16:D18" si="33">IF($C16="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C16,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11337,13 +11749,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="27" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="D17" s="28" t="str">
         <f t="shared" ref="D17:D18" si="37">IF($C17="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C17,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11368,13 +11780,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="27" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="D18" s="28" t="str">
         <f t="shared" ref="D18" si="41">IF($C18="","",_xlfn.LET(_xlpm.h,SUBSTITUTE($C18,"#",""),_xlpm.r,HEX2DEC(LEFT(_xlpm.h,2)),_xlpm.g,HEX2DEC(MID(_xlpm.h,3,2)),_xlpm.b,HEX2DEC(RIGHT(_xlpm.h,2)),_xlpm.p,D$6,"#"&amp;DEC2HEX(ROUND(_xlpm.r*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.g*(1-_xlpm.p),0),2)&amp;DEC2HEX(ROUND(_xlpm.b*(1-_xlpm.p),0),2)))</f>
@@ -11399,138 +11811,138 @@
     </row>
     <row r="21" spans="1:8" ht="30.75">
       <c r="A21" s="32" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>351</v>
+        <v>385</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="30.75">
       <c r="A22" s="33" t="s">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="30.75">
       <c r="A23" s="33" t="s">
-        <v>242</v>
+        <v>26</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="30.75">
       <c r="A24" s="33" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="30.75">
       <c r="A25" s="33" t="s">
-        <v>227</v>
+        <v>37</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30.75">
       <c r="A26" s="33" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="30.75">
       <c r="A27" s="33" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="30.75">
       <c r="A28" s="33" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
